--- a/www/download/IND.empe.s.un.zdW16.xlsx
+++ b/www/download/IND.empe.s.un.zdW16.xlsx
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Number of employee</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.847</t>
+          <t>7846822</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7.942</t>
+          <t>7941822</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.209</t>
+          <t>8209062</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8.387</t>
+          <t>8387498</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>8669636</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>8.936</t>
+          <t>8936111</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>9.288</t>
+          <t>9288117</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>9.556</t>
+          <t>9555910</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>9.668</t>
+          <t>9668055</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>9.778</t>
+          <t>9777682</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.039</t>
+          <t>10039231</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>10.304</t>
+          <t>10303768</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>10.415</t>
+          <t>10415453</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>10.454</t>
+          <t>10454435</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>10.669</t>
+          <t>10668544</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.245</t>
+          <t>3245220</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.267</t>
+          <t>3266550</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3259580</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3.277</t>
+          <t>3276810</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3.292</t>
+          <t>3291560</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3.329</t>
+          <t>3329350</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3.385</t>
+          <t>3385420</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3.454</t>
+          <t>3454200</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3.521</t>
+          <t>3520560</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3.497</t>
+          <t>3496720</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>3.527</t>
+          <t>3527070</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3.592</t>
+          <t>3591660</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3.643</t>
+          <t>3642810</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3.665</t>
+          <t>3664940</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.697</t>
+          <t>3696920</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>3407400</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3469600</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.468</t>
+          <t>3468100</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3.465</t>
+          <t>3464900</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3.503</t>
+          <t>3503200</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3.561</t>
+          <t>3560600</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3.604</t>
+          <t>3603900</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>3.669</t>
+          <t>3668600</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3.737</t>
+          <t>3737300</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3.724</t>
+          <t>3723900</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>3.748</t>
+          <t>3747700</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>3.801</t>
+          <t>3800600</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3.809</t>
+          <t>3808800</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>3.785</t>
+          <t>3784800</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3.795</t>
+          <t>3795100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.397</t>
+          <t>2396910</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.361</t>
+          <t>2361460</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.364</t>
+          <t>2364220</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.444</t>
+          <t>2444140</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.509</t>
+          <t>2508610</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2589740</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.718</t>
+          <t>2718030</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.831</t>
+          <t>2830980</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.902</t>
+          <t>2901670</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.847</t>
+          <t>2846840</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2.696</t>
+          <t>2695930</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>2.642</t>
+          <t>2642340</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2.576</t>
+          <t>2576470</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2.556</t>
+          <t>2555840</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.685</t>
+          <t>2685060</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>67.891</t>
+          <t>67890575</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>68.934</t>
+          <t>68933972</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>70.713</t>
+          <t>70712537</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>74.53</t>
+          <t>74530299</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>78.471</t>
+          <t>78470729</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>81.918</t>
+          <t>81918006</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>84.17</t>
+          <t>84170411</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>87.965</t>
+          <t>87965205</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>87.419</t>
+          <t>87419319</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>84.512</t>
+          <t>84511742</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>85.825</t>
+          <t>85824641</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>88.105</t>
+          <t>88104676</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>88.016</t>
+          <t>88016228</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>92.733</t>
+          <t>92732926</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>93.704</t>
+          <t>93703726</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13.467</t>
+          <t>13466891</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13.719</t>
+          <t>13718815</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14.065</t>
+          <t>14065013</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>14.389</t>
+          <t>14389043</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>14.657</t>
+          <t>14657402</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>14.873</t>
+          <t>14873169</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>15.176</t>
+          <t>15175951</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>15.525</t>
+          <t>15524680</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>16050161</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>15.236</t>
+          <t>15236297</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>15.548</t>
+          <t>15548361</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>15.737</t>
+          <t>15737409</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>15.953</t>
+          <t>15953131</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>16.185</t>
+          <t>16184573</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>16.794</t>
+          <t>16793739</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>271.888</t>
+          <t>271888104.039201</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>281.049</t>
+          <t>281049466.103956</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>290.755</t>
+          <t>290755144.457565</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>299.897</t>
+          <t>299897099.870721</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>309.413</t>
+          <t>309413174.300806</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>318.997</t>
+          <t>318996909.217022</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>327.893</t>
+          <t>327892607.245785</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>336.87</t>
+          <t>336869988.836052</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>346.221</t>
+          <t>346221461.733545</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>356.505</t>
+          <t>356504593.807384</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>363.142</t>
+          <t>363141813.939117</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>396.126</t>
+          <t>396126004.21336</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>409.87</t>
+          <t>409870043.103466</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>418.859</t>
+          <t>418859058.266992</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>426.36</t>
+          <t>426359658.693153</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>242940</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>249610</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>257020</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>264350</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>275680</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>286930</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>297860</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>311840</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>325260</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>323920</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>353150</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>356900</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>344440</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>313350</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.155</t>
+          <t>4154960</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.141</t>
+          <t>4141350</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4.123</t>
+          <t>4123220</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4.035</t>
+          <t>4035070</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4.053</t>
+          <t>4052930</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4180320</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4.234</t>
+          <t>4234110</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4329840</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>4.445</t>
+          <t>4444990</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4.336</t>
+          <t>4336140</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>4.251</t>
+          <t>4251450</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4230160</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>4255350</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>4.296</t>
+          <t>4295910</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>4.326</t>
+          <t>4326100</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>35.922</t>
+          <t>35922000</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>35.797</t>
+          <t>35797000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>35570000</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>35.078</t>
+          <t>35078000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>35.079</t>
+          <t>35079000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>34.916</t>
+          <t>34916000</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>35.152</t>
+          <t>35152000</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>35.798</t>
+          <t>35798000</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>36.353</t>
+          <t>36353000</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>36.407</t>
+          <t>36407000</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>36.533</t>
+          <t>36533000</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>37.014</t>
+          <t>37014000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37500000</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>37.869</t>
+          <t>37869000</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>38.307</t>
+          <t>38307000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.521</t>
+          <t>2521000</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.548</t>
+          <t>2548000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.543</t>
+          <t>2543000</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.526</t>
+          <t>2526000</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.514</t>
+          <t>2514000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2.557</t>
+          <t>2557000</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2.615</t>
+          <t>2615000</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2.675</t>
+          <t>2675000</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2.708</t>
+          <t>2708000</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2.631</t>
+          <t>2631000</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2.569</t>
+          <t>2569000</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2.567</t>
+          <t>2567000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2550000</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2.554</t>
+          <t>2554000</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2.575</t>
+          <t>2575000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>13.856</t>
+          <t>13855900</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14.392</t>
+          <t>14392300</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>14840100</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>15.452</t>
+          <t>15452100</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>16090500</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>16.876</t>
+          <t>16875600</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>17.702</t>
+          <t>17701600</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>18.376</t>
+          <t>18375800</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>18.451</t>
+          <t>18451100</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>17.317</t>
+          <t>17317500</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>17.048</t>
+          <t>17048400</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>16.598</t>
+          <t>16598400</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>15.817</t>
+          <t>15817000</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>15.299</t>
+          <t>15299000</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>15.495</t>
+          <t>15495300</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>538100</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>543900</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>543200</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>552200</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>544900</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>568500</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>593100</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>587600</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>593500</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>532500</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>504500</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>537800</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>535100</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>548600</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>561100</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>2018200</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.058</t>
+          <t>2058300</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.087</t>
+          <t>2087200</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2.093</t>
+          <t>2092700</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>2105200</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2140200</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.175</t>
+          <t>2174700</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.222</t>
+          <t>2222200</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.271</t>
+          <t>2271400</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.202</t>
+          <t>2202000</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2.189</t>
+          <t>2188700</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2.214</t>
+          <t>2214000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2.231</t>
+          <t>2231400</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2.221</t>
+          <t>2221100</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2.196</t>
+          <t>2195500</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>23.346</t>
+          <t>23346000</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>23.743</t>
+          <t>23743000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>23.874</t>
+          <t>23874000</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>23.875</t>
+          <t>23875000</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>23.889</t>
+          <t>23889000</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>24.035</t>
+          <t>24035000</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>24.295</t>
+          <t>24295000</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>24.649</t>
+          <t>24649000</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>24.757</t>
+          <t>24757000</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>24.435</t>
+          <t>24435000</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>24.403</t>
+          <t>24403000</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>24.517</t>
+          <t>24517000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>24.518</t>
+          <t>24518000</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>24.462</t>
+          <t>24462000</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>24.545</t>
+          <t>24545000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24.36</t>
+          <t>24360000</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>24.562</t>
+          <t>24562000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24.749</t>
+          <t>24749000</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>24.826</t>
+          <t>24826000</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25.083</t>
+          <t>25083000</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>25.395</t>
+          <t>25395000</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>25.593</t>
+          <t>25593000</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>25.752</t>
+          <t>25752000</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>25.974</t>
+          <t>25974000</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>25.474</t>
+          <t>25474000</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>25.395</t>
+          <t>25395000</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>25.475</t>
+          <t>25475000</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>25.639</t>
+          <t>25639000</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>25960000</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>26.412</t>
+          <t>26412000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.681</t>
+          <t>2680940</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2.741</t>
+          <t>2740560</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.853</t>
+          <t>2852710</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.916</t>
+          <t>2916130</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3.014</t>
+          <t>3013940</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.952</t>
+          <t>2952450</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3069920</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.151</t>
+          <t>3151190</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3.215</t>
+          <t>3214890</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3.191</t>
+          <t>3190810</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3150020</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2919820</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2.716</t>
+          <t>2715750</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2.622</t>
+          <t>2621850</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2.625</t>
+          <t>2625170</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.526</t>
+          <t>3526070</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.586</t>
+          <t>3585630</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.599</t>
+          <t>3598760</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.645</t>
+          <t>3644760</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.617</t>
+          <t>3617130</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.643</t>
+          <t>3642990</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3.681</t>
+          <t>3681300</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>3.711</t>
+          <t>3711000</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.646</t>
+          <t>3645970</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>3.564</t>
+          <t>3564320</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>3.567</t>
+          <t>3567040</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.575</t>
+          <t>3575240</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.578</t>
+          <t>3577540</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.647</t>
+          <t>3646710</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.834</t>
+          <t>3834120</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>36.469</t>
+          <t>36469234</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40.516</t>
+          <t>40516098</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>40.597</t>
+          <t>40597124</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>39.526</t>
+          <t>39526124</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>40.854</t>
+          <t>40854327</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>43.155</t>
+          <t>43155393</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>44.873</t>
+          <t>44872672</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>46550098</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>47.214</t>
+          <t>47214275</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>48.48</t>
+          <t>48479535</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>52.063</t>
+          <t>52063443</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>53.991</t>
+          <t>53990763</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>59.919</t>
+          <t>59918507</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>66.912</t>
+          <t>66911669</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>74.641</t>
+          <t>74640901</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>193.583</t>
+          <t>193583184</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>194.762</t>
+          <t>194761653</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>195.964</t>
+          <t>195963630</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>197.756</t>
+          <t>197755615</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>200.489</t>
+          <t>200488805</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>204.577</t>
+          <t>204577246</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>209.874</t>
+          <t>209874433</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>215.987</t>
+          <t>215986651</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>221.965</t>
+          <t>221964627</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>228.908</t>
+          <t>228908309</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>229.699</t>
+          <t>229699273</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>230.251</t>
+          <t>230251378</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>259.218</t>
+          <t>259217937</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>290.083</t>
+          <t>290083084</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>314.882</t>
+          <t>314881991</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1397820</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.447</t>
+          <t>1447130</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.475</t>
+          <t>1474950</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1.509</t>
+          <t>1508950</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.559</t>
+          <t>1558680</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1649690</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1.744</t>
+          <t>1743590</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>1804650</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1.779</t>
+          <t>1779470</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>1.637</t>
+          <t>1637350</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1574220</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1.554</t>
+          <t>1554330</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1.544</t>
+          <t>1543640</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1.565</t>
+          <t>1565390</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1.593</t>
+          <t>1592930</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16.665</t>
+          <t>16664700</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17.047</t>
+          <t>17046900</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>17.415</t>
+          <t>17414600</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>17.622</t>
+          <t>17622500</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>17.666</t>
+          <t>17666100</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>17960200</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>18.357</t>
+          <t>18357300</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18639700</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>18769700</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>18.544</t>
+          <t>18543900</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>18.342</t>
+          <t>18342100</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>18.426</t>
+          <t>18425500</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>18.394</t>
+          <t>18394000</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>18.082</t>
+          <t>18082200</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>18.127</t>
+          <t>18126800</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>53.892</t>
+          <t>53892139.7551</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>53.794</t>
+          <t>53793593.9653</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>53.186</t>
+          <t>53185797.4753</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>53.136</t>
+          <t>53136412.7754</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>53.316</t>
+          <t>53316390.1939</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>53.791</t>
+          <t>53790674.3277</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>54.574</t>
+          <t>54574367.9437</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>55.012</t>
+          <t>55012268.7542</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>55.06</t>
+          <t>55059953.8889</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>54.399</t>
+          <t>54398948.8792</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>54.389</t>
+          <t>54388811.8943</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>54.455</t>
+          <t>54454928.5183</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>54.275</t>
+          <t>54275048.1091</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>53.993</t>
+          <t>53992908.9363</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>53.31</t>
+          <t>53310386.6916</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10669876</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10.945</t>
+          <t>10945374</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11.444</t>
+          <t>11444049</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>11.892</t>
+          <t>11891907</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>12.389</t>
+          <t>12389196</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>12.758</t>
+          <t>12758355</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>13.181</t>
+          <t>13181273</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>13.653</t>
+          <t>13653173</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>13.969</t>
+          <t>13969017</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>14.532</t>
+          <t>14532006</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>15.036</t>
+          <t>15035517</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>15.983</t>
+          <t>15982827</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>16.821</t>
+          <t>16821021</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>17.173</t>
+          <t>17173290</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>17.547</t>
+          <t>17546653</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>1123660</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>1078390</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1114240</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.134</t>
+          <t>1134080</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1147690</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>1172200</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>1173370</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1.234</t>
+          <t>1234040</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1.259</t>
+          <t>1258720</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1159790</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1109810</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>1119290</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1132820</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1139840</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1.157</t>
+          <t>1157290</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>244270</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>260130</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>268300</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>273370</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>279590</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>287270</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>299150</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>312870</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>328150</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>331370</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>337420</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>347480</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>356000</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>366140</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>380740</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>783740</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>798490</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>820690</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.838</t>
+          <t>838250</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.843</t>
+          <t>842640</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>861250</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.911</t>
+          <t>910760</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>948510</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.946</t>
+          <t>946070</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.795</t>
+          <t>794950</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.737</t>
+          <t>737270</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>749610</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>772710</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.785</t>
+          <t>784800</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>790630</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>21.181</t>
+          <t>21180871</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20.864</t>
+          <t>20863501</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>20.909</t>
+          <t>20909301</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>22.341</t>
+          <t>22340908</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>23.175</t>
+          <t>23174735</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>23.507</t>
+          <t>23506656</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>24429904</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>24.911</t>
+          <t>24911000</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>25.334</t>
+          <t>25334166</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>24.363</t>
+          <t>24363460</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>24.702</t>
+          <t>24701857</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>25.135</t>
+          <t>25135261</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>25.699</t>
+          <t>25699403</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>25.45</t>
+          <t>25450373</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>25.686</t>
+          <t>25685802</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132770</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133010</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134380</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134200</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>132790</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135300</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134980</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>139060</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>147340</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>142280</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>150260</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156140</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>156380</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>160800</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171630</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6.947</t>
+          <t>6947000</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7.115</t>
+          <t>7115000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>7.166</t>
+          <t>7166000</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>7.129</t>
+          <t>7129000</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>7020000</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>7.045</t>
+          <t>7045000</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7.178</t>
+          <t>7178000</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>7.383</t>
+          <t>7383000</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>7.518</t>
+          <t>7518000</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>7.441</t>
+          <t>7441000</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>7.383</t>
+          <t>7383000</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>7.429</t>
+          <t>7429000</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>7.381</t>
+          <t>7381000</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>7.259</t>
+          <t>7259000</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>7.228</t>
+          <t>7228000</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>10.601</t>
+          <t>10601000</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10.347</t>
+          <t>10346500</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>9980500</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>9.891</t>
+          <t>9891400</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>10.077</t>
+          <t>10077100</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>10.434</t>
+          <t>10433800</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>10.948</t>
+          <t>10947800</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>11.593</t>
+          <t>11592700</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>12.152</t>
+          <t>12151900</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>12.218</t>
+          <t>12218400</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>11.876</t>
+          <t>11876000</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>11.954</t>
+          <t>11953700</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>12.055</t>
+          <t>12055200</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>12.101</t>
+          <t>12100800</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>12.311</t>
+          <t>12310800</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.029</t>
+          <t>4028660</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>4.091</t>
+          <t>4090790</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4.133</t>
+          <t>4132860</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4.088</t>
+          <t>4088270</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4.102</t>
+          <t>4102200</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>4103270</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>4.142</t>
+          <t>4141640</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>4.167</t>
+          <t>4166620</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>4.191</t>
+          <t>4190840</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4.092</t>
+          <t>4091690</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>4.066</t>
+          <t>4066270</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>3.985</t>
+          <t>3985340</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>3.795</t>
+          <t>3795360</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>3.711</t>
+          <t>3711110</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>3.794</t>
+          <t>3793770</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5.846</t>
+          <t>5846400</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5.772</t>
+          <t>5771600</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6.134</t>
+          <t>6134400</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>5900100</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>6.408</t>
+          <t>6407600</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>6.162</t>
+          <t>6161600</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6.404</t>
+          <t>6403900</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>6.437</t>
+          <t>6437000</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>6.501</t>
+          <t>6501100</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>6.245</t>
+          <t>6244700</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>6.012</t>
+          <t>6012300</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>6.133</t>
+          <t>6132800</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>5.895</t>
+          <t>5895000</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>5.897</t>
+          <t>5897400</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>6.171</t>
+          <t>6170700</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>61.676</t>
+          <t>61676468</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>61.586</t>
+          <t>61586339</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>61.853</t>
+          <t>61852821</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>62.315</t>
+          <t>62314918</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>62.536</t>
+          <t>62536471</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>63.509</t>
+          <t>63509141</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>63.876</t>
+          <t>63875706</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>64549506</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>64.781</t>
+          <t>64780717</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>62.384</t>
+          <t>62384215</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>62.203</t>
+          <t>62202730</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>61.953</t>
+          <t>61952746</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>62.965</t>
+          <t>62964781</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>61070277</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>60.265</t>
+          <t>60265168</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1.812</t>
+          <t>1812030</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1.827</t>
+          <t>1827500</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1.823</t>
+          <t>1822540</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1.826</t>
+          <t>1825940</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>1784880</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>1799360</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1833190</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1.861</t>
+          <t>1861310</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1.901</t>
+          <t>1900600</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1.838</t>
+          <t>1837620</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1.809</t>
+          <t>1808730</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1854260</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1.864</t>
+          <t>1864240</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1.855</t>
+          <t>1854630</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1.896</t>
+          <t>1895540</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>740270</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>753080</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>769150</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.768</t>
+          <t>767820</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>771750</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>769370</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>782610</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>810710</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>832850</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>810640</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.789</t>
+          <t>788680</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>772690</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>762720</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.741</t>
+          <t>740590</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>744870</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.025</t>
+          <t>4025000</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4.126</t>
+          <t>4126000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4.136</t>
+          <t>4136000</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4.131</t>
+          <t>4131000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4.093</t>
+          <t>4093000</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4.109</t>
+          <t>4109000</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4.176</t>
+          <t>4176000</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4.271</t>
+          <t>4271000</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4.324</t>
+          <t>4324000</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4.209</t>
+          <t>4209000</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>4.247</t>
+          <t>4247000</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>4.353</t>
+          <t>4353000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>4.394</t>
+          <t>4394000</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>4.442</t>
+          <t>4442000</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>4.518</t>
+          <t>4518000</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>12.053</t>
+          <t>12052551</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11.703</t>
+          <t>11702944</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>11.718</t>
+          <t>11718445</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>11.699</t>
+          <t>11698834</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>11.965</t>
+          <t>11964755</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>12.602</t>
+          <t>12601501</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>12.595</t>
+          <t>12595433</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>12.675</t>
+          <t>12675200</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>13.089</t>
+          <t>13088538</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>12.962</t>
+          <t>12962492</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>13.756</t>
+          <t>13756083</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>14.621</t>
+          <t>14620651</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>16.017</t>
+          <t>16017285</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>17.707</t>
+          <t>17706570</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>20.049</t>
+          <t>20048666</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6.811</t>
+          <t>6811019</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6.605</t>
+          <t>6604821</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6.545</t>
+          <t>6544676</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6.747</t>
+          <t>6746816</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>7.011</t>
+          <t>7010524</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>7.166</t>
+          <t>7165789</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>7.343</t>
+          <t>7342516</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>7.514</t>
+          <t>7513642</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>7.657</t>
+          <t>7656534</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>7.475</t>
+          <t>7475374</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>7.714</t>
+          <t>7713909</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>7.959</t>
+          <t>7958870</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>8.072</t>
+          <t>8072284</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>8.169</t>
+          <t>8169086</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>8.308</t>
+          <t>8308333</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>139.709</t>
+          <t>139708720</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>139.748</t>
+          <t>139748079</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>138.781</t>
+          <t>138781242</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>137.829</t>
+          <t>137828936</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>139.223</t>
+          <t>139223172</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>141.123</t>
+          <t>141123281</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>144.012</t>
+          <t>144011681</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>144.797</t>
+          <t>144797053</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>144.175</t>
+          <t>144175157</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>137.692</t>
+          <t>137691709</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>136.526</t>
+          <t>136525621</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>138.029</t>
+          <t>138029303</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>140.695</t>
+          <t>140694704</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>143.158</t>
+          <t>143158280</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>145.951</t>
+          <t>145950866</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>409.877</t>
+          <t>409877307.313451</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>422.385</t>
+          <t>422385264.539941</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>434.77</t>
+          <t>434769911.890637</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>449.701</t>
+          <t>449700620.60404</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>467.937</t>
+          <t>467937284.773746</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>481.536</t>
+          <t>481536251.438879</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>498.298</t>
+          <t>498297940.266659</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>515.048</t>
+          <t>515048032.532131</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>530.111</t>
+          <t>530111243.523405</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>541.019</t>
+          <t>541019478.619352</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>554.202</t>
+          <t>554201516.714572</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>584.006</t>
+          <t>584006283.404593</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>623.348</t>
+          <t>623347582.233643</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>661.666</t>
+          <t>661665666.749006</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>695.348</t>
+          <t>695348139.974701</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1490.31</t>
+          <t>1490310314.10775</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1519.61</t>
+          <t>1519610132.6092</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1545.867</t>
+          <t>1545867256.8235</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1576.687</t>
+          <t>1576686892.25016</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1618.442</t>
+          <t>1618442200.26845</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1658.923</t>
+          <t>1658922526.9836</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1703.912</t>
+          <t>1703911765.45614</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>1749.108</t>
+          <t>1749107873.12238</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1783.849</t>
+          <t>1783849180.14585</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1795.767</t>
+          <t>1795766685.30594</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1820.797</t>
+          <t>1820797014.54799</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1893.274</t>
+          <t>1893274184.13625</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1987.338</t>
+          <t>1987337711.44621</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2079.439</t>
+          <t>2079439408.9523</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2161.813</t>
+          <t>2161813265.35945</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>1.247</t>
+          <t>1246580</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>1220730</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1.238</t>
+          <t>1237580</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>1273640</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>1278650</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>1.298</t>
+          <t>1298300</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1320890</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>1.356</t>
+          <t>1356290</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>1.401</t>
+          <t>1400680</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>1391280</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1317620</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>1268620</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>1253810</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1.246</t>
+          <t>1245980</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1.304</t>
+          <t>1303560</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3.332</t>
+          <t>3332012</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3.425</t>
+          <t>3424880</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3.451</t>
+          <t>3451203</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>3.431</t>
+          <t>3431181</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>3.448</t>
+          <t>3448279</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>3.466</t>
+          <t>3465754</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>3.541</t>
+          <t>3540633</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>3.647</t>
+          <t>3646755</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>3.724</t>
+          <t>3723895</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>3.742</t>
+          <t>3742223</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>3.828</t>
+          <t>3827566</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>4.002</t>
+          <t>4001636</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4059764</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>4.109</t>
+          <t>4108782</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>4.161</t>
+          <t>4160711</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2.155</t>
+          <t>2155000</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2.159</t>
+          <t>2159000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2.171</t>
+          <t>2171000</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2.144</t>
+          <t>2144000</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2.156</t>
+          <t>2156000</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2.193</t>
+          <t>2193000</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2270000</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2.374</t>
+          <t>2374000</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2.464</t>
+          <t>2464000</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2.443</t>
+          <t>2443000</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2.442</t>
+          <t>2442000</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2.476</t>
+          <t>2476000</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2.526</t>
+          <t>2526000</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2.562</t>
+          <t>2562000</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2.588</t>
+          <t>2588000</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4687,12 +4692,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Number of employee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
